--- a/貴賓名單範本.xlsx
+++ b/貴賓名單範本.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -448,7 +448,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -501,17 +501,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>接送人員</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>車號</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>接送地點</t>
+          <t>唱名順序</t>
         </is>
       </c>
     </row>
@@ -554,20 +544,8 @@
           <t>第1桌</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>王師傅</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ABC-1288</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>台北車站 東三門</t>
-        </is>
+      <c r="J2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -609,6 +587,9 @@
           <t>第1桌</t>
         </is>
       </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -649,6 +630,9 @@
           <t>第1桌</t>
         </is>
       </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -694,20 +678,8 @@
           <t>代理人：範例代理</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>林大哥</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>BDF-3350</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>松山機場</t>
-        </is>
+      <c r="J5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -748,6 +720,9 @@
         <is>
           <t>第2桌</t>
         </is>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1175,7 +1150,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2. 「桌次/座位」會在報到時顯示給貴賓（例：第1桌）。</t>
+          <t>3. 「序」是名單的編號；主持人唱名的順序請看「唱名順序」欄。</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1192,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6. 「接送人員」「車號」「接送地點」為選填：有填的貴賓才會出現在「交通組」畫面（只看得到自己負責的接送資料）。</t>
+          <t>6. 「唱名順序」為選填：填數字（1 最先），主持人唱名畫面就會依這個順序排列；沒填的貴賓不會出現在主持人畫面，也可以之後在後台或舞台組畫面再排。重新匯入時，沒填就保留系統裡原本排好的順序。</t>
         </is>
       </c>
     </row>
